--- a/research/traditional_assets/database/data/hungary/hungary_power.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_power.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0032</v>
+        <v>-0.0352</v>
       </c>
       <c r="G2">
-        <v>-0.3852459016393442</v>
+        <v>-0.8345864661654135</v>
       </c>
       <c r="H2">
-        <v>-0.3852459016393442</v>
+        <v>-0.8345864661654135</v>
       </c>
       <c r="I2">
-        <v>-0.6844262295081968</v>
+        <v>-1.105263157894737</v>
       </c>
       <c r="J2">
-        <v>-0.6844262295081968</v>
+        <v>-1.105263157894737</v>
       </c>
       <c r="K2">
-        <v>-1.94</v>
+        <v>-0.57</v>
       </c>
       <c r="L2">
-        <v>-0.7950819672131147</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="M2">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8945454545454545</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-1.268041237113402</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>2.46</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="V2">
-        <v>0.890909090909091</v>
+        <v>1.016233766233766</v>
       </c>
       <c r="W2">
-        <v>-0.1243589743589744</v>
+        <v>-0.07383419689119171</v>
       </c>
       <c r="X2">
-        <v>0.08248989851278665</v>
+        <v>0.07287471270272997</v>
       </c>
       <c r="Y2">
-        <v>-0.206848872871761</v>
+        <v>-0.1467089095939217</v>
       </c>
       <c r="Z2">
-        <v>0.1733323861618243</v>
+        <v>0.2373304782298358</v>
       </c>
       <c r="AA2">
-        <v>-0.1186332315123961</v>
+        <v>-0.2623126338329764</v>
       </c>
       <c r="AB2">
-        <v>0.08176351555329152</v>
+        <v>0.0725828794143597</v>
       </c>
       <c r="AC2">
-        <v>-0.2003967470656876</v>
+        <v>-0.3348955132473361</v>
       </c>
       <c r="AD2">
-        <v>0.19</v>
+        <v>0.121</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.19</v>
+        <v>0.121</v>
       </c>
       <c r="AG2">
-        <v>-2.26</v>
+        <v>-3.009</v>
       </c>
       <c r="AH2">
-        <v>0.06462585034013606</v>
+        <v>0.03780068728522337</v>
       </c>
       <c r="AI2">
-        <v>0.02322738386308068</v>
+        <v>0.01488131841101955</v>
       </c>
       <c r="AJ2">
-        <v>-4.612244897959187</v>
+        <v>-42.38028169014074</v>
       </c>
       <c r="AK2">
-        <v>-0.3944153577661431</v>
+        <v>-0.6016796640671866</v>
       </c>
       <c r="AL2">
-        <v>0.045</v>
+        <v>0.022</v>
       </c>
       <c r="AM2">
-        <v>-0.062</v>
+        <v>-0.189</v>
       </c>
       <c r="AN2">
-        <v>-0.1319444444444444</v>
+        <v>-0.1016806722689076</v>
       </c>
       <c r="AO2">
-        <v>-37.11111111111111</v>
+        <v>-66.81818181818183</v>
       </c>
       <c r="AP2">
-        <v>1.569444444444445</v>
+        <v>2.528571428571428</v>
       </c>
       <c r="AQ2">
-        <v>26.93548387096774</v>
+        <v>7.777777777777778</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0032</v>
+        <v>-0.0352</v>
       </c>
       <c r="G3">
-        <v>-0.3852459016393442</v>
+        <v>-0.8345864661654135</v>
       </c>
       <c r="H3">
-        <v>-0.3852459016393442</v>
+        <v>-0.8345864661654135</v>
       </c>
       <c r="I3">
-        <v>-0.6844262295081968</v>
+        <v>-1.105263157894737</v>
       </c>
       <c r="J3">
-        <v>-0.6844262295081968</v>
+        <v>-1.105263157894737</v>
       </c>
       <c r="K3">
-        <v>-1.94</v>
+        <v>-0.57</v>
       </c>
       <c r="L3">
-        <v>-0.7950819672131147</v>
+        <v>-0.4285714285714285</v>
       </c>
       <c r="M3">
-        <v>2.46</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.8945454545454545</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-1.268041237113402</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.46</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.45</v>
+        <v>3.13</v>
       </c>
       <c r="V3">
-        <v>0.890909090909091</v>
+        <v>1.016233766233766</v>
       </c>
       <c r="W3">
-        <v>-0.1243589743589744</v>
+        <v>-0.07383419689119171</v>
       </c>
       <c r="X3">
-        <v>0.08248989851278665</v>
+        <v>0.07287471270272997</v>
       </c>
       <c r="Y3">
-        <v>-0.206848872871761</v>
+        <v>-0.1467089095939217</v>
       </c>
       <c r="Z3">
-        <v>0.1733323861618243</v>
+        <v>0.2373304782298358</v>
       </c>
       <c r="AA3">
-        <v>-0.1186332315123961</v>
+        <v>-0.2623126338329764</v>
       </c>
       <c r="AB3">
-        <v>0.08176351555329152</v>
+        <v>0.0725828794143597</v>
       </c>
       <c r="AC3">
-        <v>-0.2003967470656876</v>
+        <v>-0.3348955132473361</v>
       </c>
       <c r="AD3">
-        <v>0.19</v>
+        <v>0.121</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.19</v>
+        <v>0.121</v>
       </c>
       <c r="AG3">
-        <v>-2.26</v>
+        <v>-3.009</v>
       </c>
       <c r="AH3">
-        <v>0.06462585034013606</v>
+        <v>0.03780068728522337</v>
       </c>
       <c r="AI3">
-        <v>0.02322738386308068</v>
+        <v>0.01488131841101955</v>
       </c>
       <c r="AJ3">
-        <v>-4.612244897959187</v>
+        <v>-42.38028169014074</v>
       </c>
       <c r="AK3">
-        <v>-0.3944153577661431</v>
+        <v>-0.6016796640671866</v>
       </c>
       <c r="AL3">
-        <v>0.045</v>
+        <v>0.022</v>
       </c>
       <c r="AM3">
-        <v>-0.062</v>
+        <v>-0.189</v>
       </c>
       <c r="AN3">
-        <v>-0.1319444444444444</v>
+        <v>-0.1016806722689076</v>
       </c>
       <c r="AO3">
-        <v>-37.11111111111111</v>
+        <v>-66.81818181818183</v>
       </c>
       <c r="AP3">
-        <v>1.569444444444445</v>
+        <v>2.528571428571428</v>
       </c>
       <c r="AQ3">
-        <v>26.93548387096774</v>
+        <v>7.777777777777778</v>
       </c>
     </row>
   </sheetData>
